--- a/artfynd/A 16398-2023 artfynd.xlsx
+++ b/artfynd/A 16398-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16398-2023 artfynd.xlsx
+++ b/artfynd/A 16398-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>109244032</v>
       </c>
       <c r="B4" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621682.0151031383</v>
+        <v>621682</v>
       </c>
       <c r="R4" t="n">
-        <v>6899035.695865795</v>
+        <v>6899036</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +972,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 16398-2023 artfynd.xlsx
+++ b/artfynd/A 16398-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109244036</v>
+        <v>109244030</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621649.2403410788</v>
+        <v>621699</v>
       </c>
       <c r="R2" t="n">
-        <v>6899101.303306364</v>
+        <v>6899040</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109244033</v>
+        <v>109244048</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621741.3587053492</v>
+        <v>621737</v>
       </c>
       <c r="R3" t="n">
-        <v>6898998.605886353</v>
+        <v>6899318</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109244032</v>
+        <v>109244036</v>
       </c>
       <c r="B4" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621682</v>
+        <v>621649</v>
       </c>
       <c r="R4" t="n">
-        <v>6899036</v>
+        <v>6899102</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109244047</v>
+        <v>109244045</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621717.8239619727</v>
+        <v>621656</v>
       </c>
       <c r="R5" t="n">
-        <v>6899287.33519924</v>
+        <v>6899266</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,19 +1034,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109244030</v>
+        <v>109244049</v>
       </c>
       <c r="B6" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621698.6977626623</v>
+        <v>621771</v>
       </c>
       <c r="R6" t="n">
-        <v>6899040.035367078</v>
+        <v>6899326</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,19 +1131,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109244057</v>
+        <v>109244052</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621822.6427541953</v>
+        <v>621779</v>
       </c>
       <c r="R7" t="n">
-        <v>6899208.45791482</v>
+        <v>6899402</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,19 +1228,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109244043</v>
+        <v>109244034</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621637.8839314849</v>
+        <v>621716</v>
       </c>
       <c r="R8" t="n">
-        <v>6899273.237304595</v>
+        <v>6898979</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1410,19 +1325,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109244048</v>
+        <v>109244047</v>
       </c>
       <c r="B9" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1489,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621737.2810183252</v>
+        <v>621718</v>
       </c>
       <c r="R9" t="n">
-        <v>6899318.396387164</v>
+        <v>6899287</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,19 +1422,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109244055</v>
+        <v>109244050</v>
       </c>
       <c r="B10" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621768.8773966439</v>
+        <v>621798</v>
       </c>
       <c r="R10" t="n">
-        <v>6899194.836726094</v>
+        <v>6899323</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,19 +1519,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109244037</v>
+        <v>109244051</v>
       </c>
       <c r="B11" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621662.6816558368</v>
+        <v>621804</v>
       </c>
       <c r="R11" t="n">
-        <v>6899117.669247293</v>
+        <v>6899413</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1746,19 +1616,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109244039</v>
+        <v>109244057</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>621648.9491673433</v>
+        <v>621822</v>
       </c>
       <c r="R12" t="n">
-        <v>6899122.310850631</v>
+        <v>6899208</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1858,19 +1713,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1897,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109244031</v>
+        <v>109244032</v>
       </c>
       <c r="B13" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>621682.0151031383</v>
+        <v>621682</v>
       </c>
       <c r="R13" t="n">
-        <v>6899035.695865795</v>
+        <v>6899036</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,19 +1810,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109244058</v>
+        <v>109244031</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>621753.8060019914</v>
+        <v>621682</v>
       </c>
       <c r="R14" t="n">
-        <v>6899210.63871882</v>
+        <v>6899036</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2082,24 +1907,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>50-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109244056</v>
+        <v>109244053</v>
       </c>
       <c r="B15" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>621821.9616278587</v>
+        <v>621708</v>
       </c>
       <c r="R15" t="n">
-        <v>6899201.427414183</v>
+        <v>6899318</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2199,19 +2004,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109244049</v>
+        <v>109244055</v>
       </c>
       <c r="B16" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>621770.2268430473</v>
+        <v>621768</v>
       </c>
       <c r="R16" t="n">
-        <v>6899325.659242725</v>
+        <v>6899195</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2311,19 +2101,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2350,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109244053</v>
+        <v>109244033</v>
       </c>
       <c r="B17" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>621708.3030639938</v>
+        <v>621741</v>
       </c>
       <c r="R17" t="n">
-        <v>6899317.81584325</v>
+        <v>6898998</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2423,19 +2198,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109244034</v>
+        <v>109244038</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>621716.3393947326</v>
+        <v>621671</v>
       </c>
       <c r="R18" t="n">
-        <v>6898979.018041767</v>
+        <v>6899110</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2535,19 +2295,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2574,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109244044</v>
+        <v>109244039</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>621661.1941676497</v>
+        <v>621648</v>
       </c>
       <c r="R19" t="n">
-        <v>6899262.403307476</v>
+        <v>6899122</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2647,19 +2392,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,15 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109244046</v>
+        <v>109244041</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>621680.1150313037</v>
+        <v>621642</v>
       </c>
       <c r="R20" t="n">
-        <v>6899256.548337563</v>
+        <v>6899127</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2759,19 +2489,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2798,37 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109244050</v>
+        <v>109244042</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>621798.3886242906</v>
+        <v>621635</v>
       </c>
       <c r="R21" t="n">
-        <v>6899322.941515793</v>
+        <v>6899138</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2871,19 +2586,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2910,37 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109244045</v>
+        <v>109244043</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>621655.9041513129</v>
+        <v>621637</v>
       </c>
       <c r="R22" t="n">
-        <v>6899266.415596767</v>
+        <v>6899273</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2983,19 +2683,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3022,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109244042</v>
+        <v>109244044</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3062,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>621634.8123295079</v>
+        <v>621661</v>
       </c>
       <c r="R23" t="n">
-        <v>6899138.147455518</v>
+        <v>6899263</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3095,19 +2780,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3134,15 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109244038</v>
+        <v>109244046</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>621670.8927433854</v>
+        <v>621681</v>
       </c>
       <c r="R24" t="n">
-        <v>6899110.492840086</v>
+        <v>6899257</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3207,19 +2877,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3246,37 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109244052</v>
+        <v>109244058</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621779.1548604238</v>
+        <v>621753</v>
       </c>
       <c r="R25" t="n">
-        <v>6899402.108808283</v>
+        <v>6899210</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3319,19 +2974,14 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50-tal bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3358,37 +3008,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109244051</v>
+        <v>109244037</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3398,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>621804.0071955407</v>
+        <v>621663</v>
       </c>
       <c r="R26" t="n">
-        <v>6899413.2824212</v>
+        <v>6899118</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3431,19 +3076,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,37 +3105,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109244041</v>
+        <v>109244056</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3510,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>621641.7566898679</v>
+        <v>621822</v>
       </c>
       <c r="R27" t="n">
-        <v>6899127.188747955</v>
+        <v>6899202</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3543,19 +3173,9 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 16398-2023 artfynd.xlsx
+++ b/artfynd/A 16398-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244030</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244048</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244036</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244045</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244049</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244052</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244034</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244047</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244050</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244051</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244057</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244032</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244031</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244053</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244055</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244033</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244038</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244039</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244041</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244042</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244043</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244044</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244046</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244058</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244037</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,8 +3329,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109244056</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>